--- a/Curs Oficial/sesiuni/s05/echipa_albastru/Produse.xlsx
+++ b/Curs Oficial/sesiuni/s05/echipa_albastru/Produse.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dim_Produse" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produse" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -543,7 +543,7 @@
         <v>349</v>
       </c>
       <c r="H4" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -584,7 +584,7 @@
         <v>145</v>
       </c>
       <c r="H5" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
         <v>279</v>
       </c>
       <c r="H6" t="n">
-        <v>6.48</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -647,7 +647,6 @@
           <t>Diagnoza computerizata</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Diagnoza</t>
@@ -662,7 +661,7 @@
         <v>189</v>
       </c>
       <c r="H7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -705,7 +704,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -746,7 +745,7 @@
         <v>420</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4</v>
+        <v>8.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -787,7 +786,7 @@
         <v>310</v>
       </c>
       <c r="H10" t="n">
-        <v>8.42</v>
+        <v>1.8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -828,7 +827,7 @@
         <v>580</v>
       </c>
       <c r="H11" t="n">
-        <v>3.97</v>
+        <v>17.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -869,7 +868,7 @@
         <v>199</v>
       </c>
       <c r="H12" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -891,7 +890,6 @@
           <t>Filtru aer</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Filtre</t>
@@ -906,7 +904,7 @@
         <v>89</v>
       </c>
       <c r="H13" t="n">
-        <v>8.880000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -945,7 +943,7 @@
         <v>1890</v>
       </c>
       <c r="H14" t="n">
-        <v>10.51</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -986,7 +984,7 @@
         <v>450</v>
       </c>
       <c r="H15" t="n">
-        <v>1.55</v>
+        <v>12</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1027,7 +1025,7 @@
         <v>990</v>
       </c>
       <c r="H16" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1068,7 +1066,7 @@
         <v>65</v>
       </c>
       <c r="H17" t="n">
-        <v>2.05</v>
+        <v>0.1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1109,7 +1107,7 @@
         <v>120</v>
       </c>
       <c r="H18" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1150,7 +1148,7 @@
         <v>95</v>
       </c>
       <c r="H19" t="n">
-        <v>2.02</v>
+        <v>5.3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1191,7 +1189,7 @@
         <v>99</v>
       </c>
       <c r="H20" t="n">
-        <v>6.89</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1232,7 +1230,7 @@
         <v>78</v>
       </c>
       <c r="H21" t="n">
-        <v>10.36</v>
+        <v>0.6</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1246,14 +1244,6 @@
           <t>Categorii: fill-down manual daca lipseste</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
